--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-05-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-05-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סקינרד You got this</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%a7%d7%99%d7%a0%d7%a8%d7%93-you-got-this/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%90%d7%94-%d7%a7%d7%90%d7%94%d7%9f-the-great-divide/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הרכב הרגאיי-מטאל מניופורט, סקינרד Skindred, מוכרים כלהקה חיה סוחפת במיוחד, אבל האלבום “Smile” מ-2023 שינה את כללי המשחק. הוא הגיע למקום השני במצעדים בבריטניה, הוביל להופעת סולד אאוט באולם וומבלי ארנה, ולזכייה גאה בפרס להקת האלטרנטיב הטובה ביותר בטקס פרסי</v>
+        <v>נואה קאהן פרסם ב־X: “מבקרים שאומרים שהאלבום ארוך מדי — לעזאזל, אני לא חושב שהוא מספיק ארוך.”בהתחשב בכך ש־The Great Divide נמשך לא פחות מ־77 דקות על פני 17 שירים, אפשר להבין מנין הביקורת מגיעה. אורך כשלעצמו אינו דבר רע.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סקינרד You got this</v>
+        <v>נואה קאהן The Great Divide</v>
       </c>
     </row>
   </sheetData>
